--- a/data/ck_dashboard_demo.xlsx
+++ b/data/ck_dashboard_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liaow\Repos\ck-project-consolidator\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eygb-my.sharepoint.com/personal/wenjun_liao_uk_ey_com/Documents/Desktop/ico_agents/code_base/ck-project-consolidator/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2760A5-2C08-452F-853E-DDED80025920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{1B2760A5-2C08-452F-853E-DDED80025920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC435A76-84A4-4C1E-8ED0-0F925FC24546}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{348ECA1E-C986-4CAC-A979-B2BB33006272}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{348ECA1E-C986-4CAC-A979-B2BB33006272}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="178">
   <si>
     <t>contract_name</t>
   </si>
@@ -556,6 +556,24 @@
   <si>
     <t>region_name</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>target_sockets_13</t>
+  </si>
+  <si>
+    <t>target_sockets_14</t>
+  </si>
+  <si>
+    <t>target_sockets_15</t>
+  </si>
+  <si>
+    <t>target_sockets_16</t>
+  </si>
+  <si>
+    <t>target_sockets_17</t>
+  </si>
+  <si>
+    <t>target_sockets_18</t>
   </si>
 </sst>
 </file>
@@ -566,21 +584,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线 Light"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -588,7 +606,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -596,7 +614,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -604,35 +622,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -640,7 +658,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -648,14 +666,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -663,14 +681,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -678,7 +696,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -686,20 +704,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1430,22 +1448,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB843356-5D5A-4D3E-8477-B7B2DD2CA9C3}">
-  <dimension ref="A1:T95"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Z95"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="39.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="39.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="13.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>171</v>
       </c>
@@ -1506,8 +1524,26 @@
       <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U1" t="s">
+        <v>172</v>
+      </c>
+      <c r="V1" t="s">
+        <v>173</v>
+      </c>
+      <c r="W1" t="s">
+        <v>174</v>
+      </c>
+      <c r="X1" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1547,7 +1583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1584,7 +1620,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1621,7 +1657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1658,7 +1694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1695,7 +1731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1732,7 +1768,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1766,7 +1802,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1797,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1828,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1859,7 +1895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1890,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1921,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1952,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1988,8 +2024,26 @@
       <c r="M15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2037,8 +2091,26 @@
       <c r="S16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U16">
+        <v>50</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2074,8 +2146,26 @@
       <c r="O17">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2111,8 +2201,26 @@
       <c r="P18">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2148,8 +2256,26 @@
       <c r="Q19">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2185,8 +2311,26 @@
       <c r="R20">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2222,8 +2366,26 @@
       <c r="S21">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -2259,8 +2421,26 @@
       <c r="T22">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2293,8 +2473,26 @@
       <c r="T23">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2324,8 +2522,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2355,8 +2571,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2422,8 +2656,26 @@
       <c r="T26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2489,8 +2741,26 @@
       <c r="T27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -2556,8 +2826,26 @@
       <c r="T28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2623,8 +2911,26 @@
       <c r="T29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U29">
+        <v>50</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -2690,8 +2996,26 @@
       <c r="T30">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>50</v>
+      </c>
+      <c r="W30">
+        <v>50</v>
+      </c>
+      <c r="X30">
+        <v>50</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2733,8 +3057,26 @@
       <c r="T31">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2764,8 +3106,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U32">
+        <v>50</v>
+      </c>
+      <c r="V32">
+        <v>50</v>
+      </c>
+      <c r="W32">
+        <v>40</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2795,8 +3155,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>50</v>
+      </c>
+      <c r="Y33">
+        <v>90</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -2838,8 +3216,26 @@
       <c r="S34">
         <v>50</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -2872,8 +3268,26 @@
       <c r="T35">
         <v>50</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U35">
+        <v>80</v>
+      </c>
+      <c r="V35">
+        <v>50</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -2903,8 +3317,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>50</v>
+      </c>
+      <c r="W36">
+        <v>50</v>
+      </c>
+      <c r="X36">
+        <v>50</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -2949,8 +3381,26 @@
       <c r="Q37">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -2986,8 +3436,26 @@
       <c r="K38">
         <v>50</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -3023,8 +3491,26 @@
       <c r="L39">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -3057,8 +3543,26 @@
       <c r="O40">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -3088,8 +3592,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>65</v>
       </c>
@@ -3120,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -3162,8 +3684,26 @@
       <c r="P43">
         <v>50</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -3205,8 +3745,26 @@
       <c r="S44">
         <v>50</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U44">
+        <v>15</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -3239,8 +3797,26 @@
       <c r="T45">
         <v>50</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U45">
+        <v>50</v>
+      </c>
+      <c r="V45">
+        <v>50</v>
+      </c>
+      <c r="W45">
+        <v>50</v>
+      </c>
+      <c r="X45">
+        <v>50</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -3282,8 +3858,26 @@
       <c r="Q46">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -3325,8 +3919,26 @@
       <c r="T47">
         <v>50</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U47">
+        <v>30</v>
+      </c>
+      <c r="V47">
+        <v>30</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -3356,8 +3968,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>50</v>
+      </c>
+      <c r="X48">
+        <v>50</v>
+      </c>
+      <c r="Y48">
+        <v>50</v>
+      </c>
+      <c r="Z48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -3399,8 +4029,26 @@
       <c r="P49">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -3442,8 +4090,26 @@
       <c r="S50">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U50">
+        <v>18</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3476,8 +4142,26 @@
       <c r="T51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U51">
+        <v>30</v>
+      </c>
+      <c r="V51">
+        <v>10</v>
+      </c>
+      <c r="W51">
+        <v>30</v>
+      </c>
+      <c r="X51">
+        <v>30</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -3507,8 +4191,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>10</v>
+      </c>
+      <c r="Y52">
+        <v>30</v>
+      </c>
+      <c r="Z52">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -3538,8 +4240,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -3578,8 +4298,26 @@
       <c r="S54">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U54">
+        <v>30</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -3609,8 +4347,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U55">
+        <v>50</v>
+      </c>
+      <c r="V55">
+        <v>50</v>
+      </c>
+      <c r="W55">
+        <v>50</v>
+      </c>
+      <c r="X55">
+        <v>50</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -3640,8 +4396,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>50</v>
+      </c>
+      <c r="X56">
+        <v>50</v>
+      </c>
+      <c r="Y56">
+        <v>50</v>
+      </c>
+      <c r="Z56">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -3674,8 +4448,26 @@
       <c r="K57">
         <v>50</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -3711,8 +4503,26 @@
       <c r="K58">
         <v>50</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -3746,7 +4556,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -3780,7 +4590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -3814,7 +4624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3850,8 +4660,26 @@
       <c r="L62">
         <v>50</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>92</v>
       </c>
@@ -3894,7 +4722,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -3930,8 +4758,26 @@
       <c r="T64">
         <v>50</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U64">
+        <v>25</v>
+      </c>
+      <c r="V64">
+        <v>25</v>
+      </c>
+      <c r="W64">
+        <v>50</v>
+      </c>
+      <c r="X64">
+        <v>50</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -3961,8 +4807,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>50</v>
+      </c>
+      <c r="X65">
+        <v>50</v>
+      </c>
+      <c r="Y65">
+        <v>50</v>
+      </c>
+      <c r="Z65">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>92</v>
       </c>
@@ -3992,8 +4856,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>50</v>
+      </c>
+      <c r="Z66">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -4036,7 +4918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>92</v>
       </c>
@@ -4072,8 +4954,26 @@
       <c r="T68">
         <v>50</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U68">
+        <v>50</v>
+      </c>
+      <c r="V68">
+        <v>50</v>
+      </c>
+      <c r="W68">
+        <v>50</v>
+      </c>
+      <c r="X68">
+        <v>50</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>92</v>
       </c>
@@ -4116,7 +5016,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -4146,8 +5046,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U70">
+        <v>50</v>
+      </c>
+      <c r="V70">
+        <v>50</v>
+      </c>
+      <c r="W70">
+        <v>50</v>
+      </c>
+      <c r="X70">
+        <v>50</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>92</v>
       </c>
@@ -4177,8 +5095,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>50</v>
+      </c>
+      <c r="X71">
+        <v>50</v>
+      </c>
+      <c r="Y71">
+        <v>50</v>
+      </c>
+      <c r="Z71">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>92</v>
       </c>
@@ -4208,8 +5144,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>50</v>
+      </c>
+      <c r="Z72">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -4252,7 +5206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>92</v>
       </c>
@@ -4288,8 +5242,26 @@
       <c r="T74">
         <v>50</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U74">
+        <v>50</v>
+      </c>
+      <c r="V74">
+        <v>50</v>
+      </c>
+      <c r="W74">
+        <v>50</v>
+      </c>
+      <c r="X74">
+        <v>50</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -4319,8 +5291,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>50</v>
+      </c>
+      <c r="X75">
+        <v>50</v>
+      </c>
+      <c r="Y75">
+        <v>50</v>
+      </c>
+      <c r="Z75">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>92</v>
       </c>
@@ -4351,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -4390,8 +5380,26 @@
       <c r="P77">
         <v>50</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>112</v>
       </c>
@@ -4430,8 +5438,26 @@
       <c r="P78">
         <v>50</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -4467,8 +5493,26 @@
       <c r="S79">
         <v>50</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U79">
+        <v>46</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>112</v>
       </c>
@@ -4510,8 +5554,26 @@
       <c r="Q80">
         <v>50</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -4542,7 +5604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -4578,8 +5640,26 @@
       <c r="T82">
         <v>50</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U82">
+        <v>50</v>
+      </c>
+      <c r="V82">
+        <v>50</v>
+      </c>
+      <c r="W82">
+        <v>50</v>
+      </c>
+      <c r="X82">
+        <v>50</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>112</v>
       </c>
@@ -4609,8 +5689,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U83">
+        <v>50</v>
+      </c>
+      <c r="V83">
+        <v>50</v>
+      </c>
+      <c r="W83">
+        <v>50</v>
+      </c>
+      <c r="X83">
+        <v>50</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -4640,8 +5738,26 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -4672,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -4703,7 +5819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>112</v>
       </c>
@@ -4734,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>112</v>
       </c>
@@ -4765,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>112</v>
       </c>
@@ -4796,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>112</v>
       </c>
@@ -4827,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>112</v>
       </c>
@@ -4869,8 +5985,26 @@
       <c r="N91">
         <v>50</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>112</v>
       </c>
@@ -4918,8 +6052,26 @@
       <c r="N92">
         <v>50</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>112</v>
       </c>
@@ -4961,8 +6113,26 @@
       <c r="N93">
         <v>50</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>140</v>
       </c>
@@ -4996,7 +6166,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>140</v>
       </c>
@@ -5040,14 +6210,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218D0F2A-9DF4-4636-BC6C-A88BFD889977}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -5094,14 +6264,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C973CA79-4E83-4C40-9692-FA8D6551B83E}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>143</v>
       </c>
@@ -5112,7 +6282,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5123,7 +6293,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5134,7 +6304,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5145,7 +6315,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>145</v>
       </c>
@@ -5154,7 +6324,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -5162,12 +6332,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -5175,7 +6345,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>148</v>
       </c>
